--- a/data/trans_bre/IQ2608_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-15,26</t>
+          <t>-15,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-19,76%</t>
+          <t>-19,77%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 6,18</t>
+          <t>-13,17; 5,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 7,69</t>
+          <t>-6,97; 7,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,28; -3,01</t>
+          <t>-17,44; -2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 2,84</t>
+          <t>-33,06; 4,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 11,56</t>
+          <t>-20,56; 10,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 9,9</t>
+          <t>-8,08; 10,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,07; -3,47</t>
+          <t>-19,22; -3,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 3,63</t>
+          <t>-40,46; 6,13</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,47</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-6,79%</t>
+          <t>-4,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 1,55</t>
+          <t>-12,77; 2,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 3,16</t>
+          <t>-8,55; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 4,95</t>
+          <t>-7,23; 4,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 10,29</t>
+          <t>-19,84; 10,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 2,84</t>
+          <t>-19,67; 4,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 3,95</t>
+          <t>-9,89; 3,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 6,3</t>
+          <t>-8,52; 5,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 13,57</t>
+          <t>-23,13; 15,32</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>-1,45%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 7,98</t>
+          <t>-10,39; 8,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 7,11</t>
+          <t>-7,76; 7,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 9,55</t>
+          <t>-1,87; 10,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 25,52</t>
+          <t>-21,31; 19,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 13,72</t>
+          <t>-15,16; 14,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 9,76</t>
+          <t>-9,8; 11,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 11,65</t>
+          <t>-2,07; 12,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 58,89</t>
+          <t>-34,05; 46,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,01%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 6,29</t>
+          <t>-8,45; 6,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 6,98</t>
+          <t>-7,05; 5,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 2,77</t>
+          <t>-11,19; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 19,14</t>
+          <t>-17,21; 16,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 9,74</t>
+          <t>-11,7; 10,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 8,89</t>
+          <t>-8,26; 7,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 3,7</t>
+          <t>-13,99; 4,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 37,81</t>
+          <t>-25,55; 32,09</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,72%</t>
+          <t>-6,6%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,13</t>
+          <t>-7,08; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,17</t>
+          <t>-4,14; 2,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,6</t>
+          <t>-6,31; 0,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 4,82</t>
+          <t>-13,67; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 1,76</t>
+          <t>-10,84; 1,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,67</t>
+          <t>-4,98; 3,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,68</t>
+          <t>-7,37; 0,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 7,66</t>
+          <t>-18,85; 7,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2608_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,93</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-15,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-11,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-19,77%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-3.925672034987071</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.489609259654844</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-10.47880910029317</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-15.10372214593582</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.06631945750795518</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.00593332466226737</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1173102744893365</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1976595206877776</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,17; 5,44</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,97; 7,97</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-17,44; -2,91</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-33,06; 4,36</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-20,56; 10,05</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-8,08; 10,3</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-19,22; -3,39</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-40,46; 6,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-13.16776803006292</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.973031204185428</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-17.44444429794895</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-33.05949080651297</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2056246383256117</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.08080636955980687</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1921684139256275</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4045849395095233</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.443807863400956</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.97371609349255</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-2.912039482592656</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.359958909736347</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1004778518278949</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1029814672663275</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-0.03391513075679164</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.06133029866971271</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-5,59</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,35</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-9,02%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-3,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,05%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-4,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-12,77; 2,34</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,55; 3,21</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 4,45</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-19,84; 10,57</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-19,67; 4,22</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-9,89; 3,96</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-8,52; 5,61</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-23,13; 15,32</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-5.587360044093181</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.736819833368476</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.8645197023864792</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.351491445789334</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.09019128377010863</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03222932943689914</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01050061685591395</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.04210426127482134</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-1,45%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-12.76567956313102</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.554661218854037</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.230056665493875</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-19.84175706198385</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1967357797365873</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.09887128722625416</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.08520297501640839</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.231324744536953</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,39; 8,19</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; 7,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 10,05</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-21,31; 19,83</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-15,16; 14,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-9,8; 11,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 12,27</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-34,05; 46,13</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.338033267282912</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.211563843202212</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.445975474810609</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.56675731398708</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.04220270962661136</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03958458517035839</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.05605334580383352</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1532411847987629</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-5,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,01%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.288188319002315</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.06970768990361975</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.078187093225727</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.7929112678596639</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.02036299615350573</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.0009172809277346567</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.04741305906395545</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.01449907707004167</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,45; 6,66</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; 5,81</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-11,19; 3,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-17,21; 16,98</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-11,7; 10,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-8,26; 7,58</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-13,99; 4,54</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-25,55; 32,09</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.39386140362395</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.758722425942806</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.870031687507954</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-21.3127022541826</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.151595179634133</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.09804019612338098</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.02074638411850792</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.340472653149424</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.186391504748819</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.9505418462342</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.04664303937576</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>19.83001484690676</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1446448160074313</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1120059855515023</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.122668384145851</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4613077103920289</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.425105277227867</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.8204117736414274</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-4.111310742960105</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.008654189989276695</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02079996923188056</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.009931906502107027</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.05300208310487124</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.0001427210474058174</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.453184419147867</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.048248320455046</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-11.19037927618761</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-17.20968812300021</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1170023252615943</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.08255884599059847</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1398687258469662</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2554544767082603</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.656496761588232</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.811474108933804</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.38498670499837</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>16.98122494706705</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1008305927065162</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.07584045352983508</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.04535055927443791</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3209344992964122</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,97</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,29%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-7,08; 1,02</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 2,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 0,31</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,67; 5,01</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-10,84; 1,64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; 3,26</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-7,37; 0,37</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,85; 7,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.972954968622632</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.9735269749811315</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.735871521137989</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.515526901115996</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.04677686431450846</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01189578354559187</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.03286502019176372</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06604070738185348</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-7.081845135924332</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.144298430373778</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.305370556775001</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.66710817466211</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1083550283610847</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04977966437748108</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.07373131052137642</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.188474352558203</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.018790818862799</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.618742798529417</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3104098169418997</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.008386819733057</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.0164088958388643</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.03263715462530749</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.003651554403977374</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.07910177876466264</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
